--- a/artfynd/A 30907-2023 artfynd.xlsx
+++ b/artfynd/A 30907-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2874,6 +2874,1116 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113680541</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91388</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Oksejaevrie, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>644010</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7086624</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113680534</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91388</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stenbittjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>644449</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7086391</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113677111</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5478</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oksejaevrie, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>644078</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7086700</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>113680537</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91388</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nybrännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>644201</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7086644</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>113680539</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91388</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oksejaevrie, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>644103</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7086718</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>113680538</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91404</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Oksejaevrie, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>644108</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7086698</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>113680536</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91432</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nybrännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>644239</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7086604</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>113680533</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91404</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stenbittjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>644446</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7086358</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113680535</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91374</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bankera fuligineoalba</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nybrännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>644359</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7086420</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>113680532</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91382</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stenbittjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>644466</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7086356</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 30907-2023 artfynd.xlsx
+++ b/artfynd/A 30907-2023 artfynd.xlsx
@@ -2879,10 +2879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113680541</v>
+        <v>113680536</v>
       </c>
       <c r="B21" t="n">
-        <v>91388</v>
+        <v>91434</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2891,38 +2891,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>644010</v>
+        <v>644239</v>
       </c>
       <c r="R21" t="n">
-        <v>7086624</v>
+        <v>7086604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113680534</v>
+        <v>113680532</v>
       </c>
       <c r="B22" t="n">
-        <v>91388</v>
+        <v>91384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3002,25 +3002,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>644449</v>
+        <v>644466</v>
       </c>
       <c r="R22" t="n">
-        <v>7086391</v>
+        <v>7086356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113677111</v>
+        <v>113680538</v>
       </c>
       <c r="B23" t="n">
-        <v>5478</v>
+        <v>91406</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101410</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>644078</v>
+        <v>644108</v>
       </c>
       <c r="R23" t="n">
-        <v>7086700</v>
+        <v>7086698</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3188,12 +3188,12 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3212,10 +3212,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113680537</v>
+        <v>113680533</v>
       </c>
       <c r="B24" t="n">
-        <v>91388</v>
+        <v>91406</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,38 +3224,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>644201</v>
+        <v>644446</v>
       </c>
       <c r="R24" t="n">
-        <v>7086644</v>
+        <v>7086358</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3326,7 +3326,7 @@
         <v>113680539</v>
       </c>
       <c r="B25" t="n">
-        <v>91388</v>
+        <v>91390</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113680538</v>
+        <v>113680534</v>
       </c>
       <c r="B26" t="n">
-        <v>91404</v>
+        <v>91390</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,38 +3446,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>644108</v>
+        <v>644449</v>
       </c>
       <c r="R26" t="n">
-        <v>7086698</v>
+        <v>7086391</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113680536</v>
+        <v>113680537</v>
       </c>
       <c r="B27" t="n">
-        <v>91432</v>
+        <v>91390</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3557,25 +3557,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>644239</v>
+        <v>644201</v>
       </c>
       <c r="R27" t="n">
-        <v>7086604</v>
+        <v>7086644</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113680533</v>
+        <v>113680541</v>
       </c>
       <c r="B28" t="n">
-        <v>91404</v>
+        <v>91390</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,38 +3668,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>644446</v>
+        <v>644010</v>
       </c>
       <c r="R28" t="n">
-        <v>7086358</v>
+        <v>7086624</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113680535</v>
+        <v>113677111</v>
       </c>
       <c r="B29" t="n">
-        <v>91374</v>
+        <v>5478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3783,34 +3783,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>101410</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>644359</v>
+        <v>644078</v>
       </c>
       <c r="R29" t="n">
-        <v>7086420</v>
+        <v>7086700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,12 +3854,12 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW29" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113680532</v>
+        <v>113680535</v>
       </c>
       <c r="B30" t="n">
-        <v>91382</v>
+        <v>91376</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>644466</v>
+        <v>644359</v>
       </c>
       <c r="R30" t="n">
-        <v>7086356</v>
+        <v>7086420</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 30907-2023 artfynd.xlsx
+++ b/artfynd/A 30907-2023 artfynd.xlsx
@@ -3767,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113677111</v>
+        <v>113680535</v>
       </c>
       <c r="B29" t="n">
-        <v>5478</v>
+        <v>91376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3783,34 +3783,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101410</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>644078</v>
+        <v>644359</v>
       </c>
       <c r="R29" t="n">
-        <v>7086700</v>
+        <v>7086420</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,12 +3854,12 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AS29" t="inlineStr">
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113680535</v>
+        <v>113677111</v>
       </c>
       <c r="B30" t="n">
-        <v>91376</v>
+        <v>5478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3100</v>
+        <v>101410</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>644359</v>
+        <v>644078</v>
       </c>
       <c r="R30" t="n">
-        <v>7086420</v>
+        <v>7086700</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,12 +3965,12 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW30" t="inlineStr">
         <is>
           <t>Helene Andersson</t>

--- a/artfynd/A 30907-2023 artfynd.xlsx
+++ b/artfynd/A 30907-2023 artfynd.xlsx
@@ -2879,10 +2879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113680536</v>
+        <v>113680538</v>
       </c>
       <c r="B21" t="n">
-        <v>91434</v>
+        <v>91406</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2895,34 +2895,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>644239</v>
+        <v>644108</v>
       </c>
       <c r="R21" t="n">
-        <v>7086604</v>
+        <v>7086698</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113680532</v>
+        <v>113680533</v>
       </c>
       <c r="B22" t="n">
-        <v>91384</v>
+        <v>91406</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3006,21 +3006,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>644466</v>
+        <v>644446</v>
       </c>
       <c r="R22" t="n">
-        <v>7086356</v>
+        <v>7086358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113680538</v>
+        <v>113680532</v>
       </c>
       <c r="B23" t="n">
-        <v>91406</v>
+        <v>91384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,34 +3117,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>644108</v>
+        <v>644466</v>
       </c>
       <c r="R23" t="n">
-        <v>7086698</v>
+        <v>7086356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3212,10 +3212,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113680533</v>
+        <v>113680539</v>
       </c>
       <c r="B24" t="n">
-        <v>91406</v>
+        <v>91390</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,38 +3224,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>644446</v>
+        <v>644103</v>
       </c>
       <c r="R24" t="n">
-        <v>7086358</v>
+        <v>7086718</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113680539</v>
+        <v>113680537</v>
       </c>
       <c r="B25" t="n">
         <v>91390</v>
@@ -3359,14 +3359,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>644103</v>
+        <v>644201</v>
       </c>
       <c r="R25" t="n">
-        <v>7086718</v>
+        <v>7086644</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113680537</v>
+        <v>113677111</v>
       </c>
       <c r="B27" t="n">
-        <v>91390</v>
+        <v>5478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3557,38 +3557,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>644201</v>
+        <v>644078</v>
       </c>
       <c r="R27" t="n">
-        <v>7086644</v>
+        <v>7086700</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3632,12 +3632,12 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW27" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113680541</v>
+        <v>113680535</v>
       </c>
       <c r="B28" t="n">
-        <v>91390</v>
+        <v>91376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,38 +3668,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>644010</v>
+        <v>644359</v>
       </c>
       <c r="R28" t="n">
-        <v>7086624</v>
+        <v>7086420</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113680535</v>
+        <v>113680541</v>
       </c>
       <c r="B29" t="n">
-        <v>91376</v>
+        <v>91390</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3779,38 +3779,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>644359</v>
+        <v>644010</v>
       </c>
       <c r="R29" t="n">
-        <v>7086420</v>
+        <v>7086624</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113677111</v>
+        <v>113680536</v>
       </c>
       <c r="B30" t="n">
-        <v>5478</v>
+        <v>91434</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101410</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>644078</v>
+        <v>644239</v>
       </c>
       <c r="R30" t="n">
-        <v>7086700</v>
+        <v>7086604</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,12 +3965,12 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AS30" t="inlineStr">
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
           <t>Helene Andersson</t>

--- a/artfynd/A 30907-2023 artfynd.xlsx
+++ b/artfynd/A 30907-2023 artfynd.xlsx
@@ -2879,10 +2879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113680538</v>
+        <v>113677111</v>
       </c>
       <c r="B21" t="n">
-        <v>91406</v>
+        <v>5478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>101410</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>644108</v>
+        <v>644078</v>
       </c>
       <c r="R21" t="n">
-        <v>7086698</v>
+        <v>7086700</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,12 +2966,12 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW21" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2993,7 +2993,7 @@
         <v>113680533</v>
       </c>
       <c r="B22" t="n">
-        <v>91406</v>
+        <v>91410</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113680532</v>
+        <v>113680534</v>
       </c>
       <c r="B23" t="n">
-        <v>91384</v>
+        <v>91394</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,25 +3113,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>644466</v>
+        <v>644449</v>
       </c>
       <c r="R23" t="n">
-        <v>7086356</v>
+        <v>7086391</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3212,10 +3212,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113680539</v>
+        <v>113680532</v>
       </c>
       <c r="B24" t="n">
-        <v>91390</v>
+        <v>91388</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,38 +3224,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>644103</v>
+        <v>644466</v>
       </c>
       <c r="R24" t="n">
-        <v>7086718</v>
+        <v>7086356</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113680537</v>
+        <v>113680536</v>
       </c>
       <c r="B25" t="n">
-        <v>91390</v>
+        <v>91438</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,25 +3335,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>644201</v>
+        <v>644239</v>
       </c>
       <c r="R25" t="n">
-        <v>7086644</v>
+        <v>7086604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113680534</v>
+        <v>113680538</v>
       </c>
       <c r="B26" t="n">
-        <v>91390</v>
+        <v>91410</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,38 +3446,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>644449</v>
+        <v>644108</v>
       </c>
       <c r="R26" t="n">
-        <v>7086391</v>
+        <v>7086698</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113677111</v>
+        <v>113680537</v>
       </c>
       <c r="B27" t="n">
-        <v>5478</v>
+        <v>91394</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3557,38 +3557,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>644078</v>
+        <v>644201</v>
       </c>
       <c r="R27" t="n">
-        <v>7086700</v>
+        <v>7086644</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3632,12 +3632,12 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AS27" t="inlineStr">
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113680535</v>
+        <v>113680539</v>
       </c>
       <c r="B28" t="n">
-        <v>91376</v>
+        <v>91394</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,38 +3668,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>644359</v>
+        <v>644103</v>
       </c>
       <c r="R28" t="n">
-        <v>7086420</v>
+        <v>7086718</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113680541</v>
+        <v>113680535</v>
       </c>
       <c r="B29" t="n">
-        <v>91390</v>
+        <v>91380</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3779,38 +3779,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>644010</v>
+        <v>644359</v>
       </c>
       <c r="R29" t="n">
-        <v>7086624</v>
+        <v>7086420</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113680536</v>
+        <v>113680541</v>
       </c>
       <c r="B30" t="n">
-        <v>91434</v>
+        <v>91394</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3890,38 +3890,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>644239</v>
+        <v>644010</v>
       </c>
       <c r="R30" t="n">
-        <v>7086604</v>
+        <v>7086624</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 30907-2023 artfynd.xlsx
+++ b/artfynd/A 30907-2023 artfynd.xlsx
@@ -2879,10 +2879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113677111</v>
+        <v>113680536</v>
       </c>
       <c r="B21" t="n">
-        <v>5478</v>
+        <v>91438</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2895,34 +2895,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101410</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>644078</v>
+        <v>644239</v>
       </c>
       <c r="R21" t="n">
-        <v>7086700</v>
+        <v>7086604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,12 +2966,12 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AS21" t="inlineStr">
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113680534</v>
+        <v>113680539</v>
       </c>
       <c r="B23" t="n">
         <v>91394</v>
@@ -3137,14 +3137,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>644449</v>
+        <v>644103</v>
       </c>
       <c r="R23" t="n">
-        <v>7086391</v>
+        <v>7086718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113680536</v>
+        <v>113680535</v>
       </c>
       <c r="B25" t="n">
-        <v>91438</v>
+        <v>91380</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,21 +3339,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>644239</v>
+        <v>644359</v>
       </c>
       <c r="R25" t="n">
-        <v>7086604</v>
+        <v>7086420</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113680538</v>
+        <v>113680541</v>
       </c>
       <c r="B26" t="n">
-        <v>91410</v>
+        <v>91394</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>644108</v>
+        <v>644010</v>
       </c>
       <c r="R26" t="n">
-        <v>7086698</v>
+        <v>7086624</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113680539</v>
+        <v>113680538</v>
       </c>
       <c r="B28" t="n">
-        <v>91394</v>
+        <v>91410</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,25 +3668,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>644103</v>
+        <v>644108</v>
       </c>
       <c r="R28" t="n">
-        <v>7086718</v>
+        <v>7086698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113680535</v>
+        <v>113677111</v>
       </c>
       <c r="B29" t="n">
-        <v>91380</v>
+        <v>5478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3783,34 +3783,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>101410</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>644359</v>
+        <v>644078</v>
       </c>
       <c r="R29" t="n">
-        <v>7086420</v>
+        <v>7086700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,12 +3854,12 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW29" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113680541</v>
+        <v>113680534</v>
       </c>
       <c r="B30" t="n">
         <v>91394</v>
@@ -3914,14 +3914,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>644010</v>
+        <v>644449</v>
       </c>
       <c r="R30" t="n">
-        <v>7086624</v>
+        <v>7086391</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 30907-2023 artfynd.xlsx
+++ b/artfynd/A 30907-2023 artfynd.xlsx
@@ -2879,10 +2879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113680536</v>
+        <v>113680541</v>
       </c>
       <c r="B21" t="n">
-        <v>91438</v>
+        <v>91394</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2891,38 +2891,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>644239</v>
+        <v>644010</v>
       </c>
       <c r="R21" t="n">
-        <v>7086604</v>
+        <v>7086624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113680533</v>
+        <v>113677111</v>
       </c>
       <c r="B22" t="n">
-        <v>91410</v>
+        <v>5478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3006,34 +3006,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>101410</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>644446</v>
+        <v>644078</v>
       </c>
       <c r="R22" t="n">
-        <v>7086358</v>
+        <v>7086700</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3077,12 +3077,12 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW22" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113680539</v>
+        <v>113680538</v>
       </c>
       <c r="B23" t="n">
-        <v>91394</v>
+        <v>91410</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,25 +3113,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>644103</v>
+        <v>644108</v>
       </c>
       <c r="R23" t="n">
-        <v>7086718</v>
+        <v>7086698</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3212,10 +3212,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113680532</v>
+        <v>113680539</v>
       </c>
       <c r="B24" t="n">
-        <v>91388</v>
+        <v>91394</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,38 +3224,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>644466</v>
+        <v>644103</v>
       </c>
       <c r="R24" t="n">
-        <v>7086356</v>
+        <v>7086718</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113680535</v>
+        <v>113680533</v>
       </c>
       <c r="B25" t="n">
-        <v>91380</v>
+        <v>91410</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,34 +3339,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>644359</v>
+        <v>644446</v>
       </c>
       <c r="R25" t="n">
-        <v>7086420</v>
+        <v>7086358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113680541</v>
+        <v>113680537</v>
       </c>
       <c r="B26" t="n">
         <v>91394</v>
@@ -3470,14 +3470,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>644010</v>
+        <v>644201</v>
       </c>
       <c r="R26" t="n">
-        <v>7086624</v>
+        <v>7086644</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113680537</v>
+        <v>113680535</v>
       </c>
       <c r="B27" t="n">
-        <v>91394</v>
+        <v>91380</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3557,25 +3557,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>644201</v>
+        <v>644359</v>
       </c>
       <c r="R27" t="n">
-        <v>7086644</v>
+        <v>7086420</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113680538</v>
+        <v>113680534</v>
       </c>
       <c r="B28" t="n">
-        <v>91410</v>
+        <v>91394</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,38 +3668,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>644108</v>
+        <v>644449</v>
       </c>
       <c r="R28" t="n">
-        <v>7086698</v>
+        <v>7086391</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113677111</v>
+        <v>113680536</v>
       </c>
       <c r="B29" t="n">
-        <v>5478</v>
+        <v>91438</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3783,34 +3783,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101410</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>644078</v>
+        <v>644239</v>
       </c>
       <c r="R29" t="n">
-        <v>7086700</v>
+        <v>7086604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,12 +3854,12 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AS29" t="inlineStr">
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113680534</v>
+        <v>113680532</v>
       </c>
       <c r="B30" t="n">
-        <v>91394</v>
+        <v>91388</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3890,25 +3890,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>644449</v>
+        <v>644466</v>
       </c>
       <c r="R30" t="n">
-        <v>7086391</v>
+        <v>7086356</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 30907-2023 artfynd.xlsx
+++ b/artfynd/A 30907-2023 artfynd.xlsx
@@ -2879,7 +2879,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113680541</v>
+        <v>113680537</v>
       </c>
       <c r="B21" t="n">
         <v>91394</v>
@@ -2915,14 +2915,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>644010</v>
+        <v>644201</v>
       </c>
       <c r="R21" t="n">
-        <v>7086624</v>
+        <v>7086644</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113677111</v>
+        <v>113680532</v>
       </c>
       <c r="B22" t="n">
-        <v>5478</v>
+        <v>91388</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3006,34 +3006,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101410</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>644078</v>
+        <v>644466</v>
       </c>
       <c r="R22" t="n">
-        <v>7086700</v>
+        <v>7086356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3077,12 +3077,12 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AS22" t="inlineStr">
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113680538</v>
+        <v>113680533</v>
       </c>
       <c r="B23" t="n">
         <v>91410</v>
@@ -3137,14 +3137,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>644108</v>
+        <v>644446</v>
       </c>
       <c r="R23" t="n">
-        <v>7086698</v>
+        <v>7086358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3212,7 +3212,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113680539</v>
+        <v>113680534</v>
       </c>
       <c r="B24" t="n">
         <v>91394</v>
@@ -3248,14 +3248,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>644103</v>
+        <v>644449</v>
       </c>
       <c r="R24" t="n">
-        <v>7086718</v>
+        <v>7086391</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113680533</v>
+        <v>113680536</v>
       </c>
       <c r="B25" t="n">
-        <v>91410</v>
+        <v>91438</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,34 +3339,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>644446</v>
+        <v>644239</v>
       </c>
       <c r="R25" t="n">
-        <v>7086358</v>
+        <v>7086604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113680537</v>
+        <v>113680541</v>
       </c>
       <c r="B26" t="n">
         <v>91394</v>
@@ -3470,14 +3470,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>644201</v>
+        <v>644010</v>
       </c>
       <c r="R26" t="n">
-        <v>7086644</v>
+        <v>7086624</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113680535</v>
+        <v>113680538</v>
       </c>
       <c r="B27" t="n">
-        <v>91380</v>
+        <v>91410</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3561,34 +3561,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>644359</v>
+        <v>644108</v>
       </c>
       <c r="R27" t="n">
-        <v>7086420</v>
+        <v>7086698</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113680534</v>
+        <v>113677111</v>
       </c>
       <c r="B28" t="n">
-        <v>91394</v>
+        <v>5478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,38 +3668,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>644449</v>
+        <v>644078</v>
       </c>
       <c r="R28" t="n">
-        <v>7086391</v>
+        <v>7086700</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3743,12 +3743,12 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW28" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113680536</v>
+        <v>113680539</v>
       </c>
       <c r="B29" t="n">
-        <v>91438</v>
+        <v>91394</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3779,38 +3779,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nybrännan, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>644239</v>
+        <v>644103</v>
       </c>
       <c r="R29" t="n">
-        <v>7086604</v>
+        <v>7086718</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113680532</v>
+        <v>113680535</v>
       </c>
       <c r="B30" t="n">
-        <v>91388</v>
+        <v>91380</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3894,34 +3894,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Nybrännan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>644466</v>
+        <v>644359</v>
       </c>
       <c r="R30" t="n">
-        <v>7086356</v>
+        <v>7086420</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 30907-2023 artfynd.xlsx
+++ b/artfynd/A 30907-2023 artfynd.xlsx
@@ -2879,10 +2879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113680537</v>
+        <v>113680536</v>
       </c>
       <c r="B21" t="n">
-        <v>91394</v>
+        <v>91438</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2891,25 +2891,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>644201</v>
+        <v>644239</v>
       </c>
       <c r="R21" t="n">
-        <v>7086644</v>
+        <v>7086604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113680532</v>
+        <v>113680539</v>
       </c>
       <c r="B22" t="n">
-        <v>91388</v>
+        <v>91394</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3002,38 +3002,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>644466</v>
+        <v>644103</v>
       </c>
       <c r="R22" t="n">
-        <v>7086356</v>
+        <v>7086718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113680533</v>
+        <v>113677111</v>
       </c>
       <c r="B23" t="n">
-        <v>91410</v>
+        <v>5478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,34 +3117,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>101410</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stenbittjärnarna, Ång</t>
+          <t>Oksejaevrie, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>644446</v>
+        <v>644078</v>
       </c>
       <c r="R23" t="n">
-        <v>7086358</v>
+        <v>7086700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3188,12 +3188,12 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
       <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW23" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3212,10 +3212,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113680534</v>
+        <v>113680533</v>
       </c>
       <c r="B24" t="n">
-        <v>91394</v>
+        <v>91410</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,25 +3224,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>644449</v>
+        <v>644446</v>
       </c>
       <c r="R24" t="n">
-        <v>7086391</v>
+        <v>7086358</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113680536</v>
+        <v>113680537</v>
       </c>
       <c r="B25" t="n">
-        <v>91438</v>
+        <v>91394</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,25 +3335,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>644239</v>
+        <v>644201</v>
       </c>
       <c r="R25" t="n">
-        <v>7086604</v>
+        <v>7086644</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113680541</v>
+        <v>113680538</v>
       </c>
       <c r="B26" t="n">
-        <v>91394</v>
+        <v>91410</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>644010</v>
+        <v>644108</v>
       </c>
       <c r="R26" t="n">
-        <v>7086624</v>
+        <v>7086698</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113680538</v>
+        <v>113680541</v>
       </c>
       <c r="B27" t="n">
-        <v>91410</v>
+        <v>91394</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3557,25 +3557,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>644108</v>
+        <v>644010</v>
       </c>
       <c r="R27" t="n">
-        <v>7086698</v>
+        <v>7086624</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113677111</v>
+        <v>113680534</v>
       </c>
       <c r="B28" t="n">
-        <v>5478</v>
+        <v>91394</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,38 +3668,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>644078</v>
+        <v>644449</v>
       </c>
       <c r="R28" t="n">
-        <v>7086700</v>
+        <v>7086391</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3743,12 +3743,12 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AS28" t="inlineStr">
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113680539</v>
+        <v>113680532</v>
       </c>
       <c r="B29" t="n">
-        <v>91394</v>
+        <v>91388</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3779,38 +3779,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oksejaevrie, Ång</t>
+          <t>Stenbittjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>644103</v>
+        <v>644466</v>
       </c>
       <c r="R29" t="n">
-        <v>7086718</v>
+        <v>7086356</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 30907-2023 artfynd.xlsx
+++ b/artfynd/A 30907-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
